--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -555,7 +555,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FIN 2010  |  Module 05  |  Financial Statement Analysis</t>
+          <t>Financial Statement Analysis</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -642,7 +642,7 @@
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ratios  -  Fourteen ratios plus the DuPont decomposition.</t>
+          <t xml:space="preserve">   Ratios  -  Fifteen ratios plus the DuPont decomposition.</t>
         </is>
       </c>
     </row>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -584,7 +584,7 @@
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>One company. Five fiscal years. You will paste in the income statement and balance sheet, then build three analyses yourself: common-size statements, a trend analysis, and a set of ratios.</t>
+          <t>One company. Five fiscal years. Statements, common-size, trend and ratios are all filled in and linked - every analysis cell is a live formula pointing at Financial Data.</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Financial Data  -  Type the five years of statements here. This is the ONLY sheet where you type numbers.</t>
+          <t xml:space="preserve">   Financial Data  -  Filled from SEC EDGAR. Every other sheet links back to it.</t>
         </is>
       </c>
     </row>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -71,7 +71,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -108,11 +108,6 @@
         <fgColor rgb="002E5C8A"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE0E0"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -140,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,7 +175,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -568,9 +562,9 @@
       <c r="I1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>Generated by edgar-query. The Financial Data sheet is already filled from SEC EDGAR; every other sheet is live formulas.</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Generated by edgar-query. The Financial Data sheet is filled from SEC EDGAR. Every other sheet is yours to build.</t>
         </is>
       </c>
     </row>
@@ -584,7 +578,7 @@
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>One company. Five fiscal years. Statements, common-size, trend and ratios are all filled in and linked - every analysis cell is a live formula pointing at Financial Data.</t>
+          <t>One company. Five fiscal years. The statements are already in front of you. What you build is the analysis: common-size statements, a trend analysis, and a set of ratios.</t>
         </is>
       </c>
     </row>
@@ -621,7 +615,7 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Financial Data  -  Filled from SEC EDGAR. Every other sheet links back to it.</t>
+          <t xml:space="preserve">   Financial Data  -  Already filled from SEC EDGAR. Read it, check it, but do not retype it.</t>
         </is>
       </c>
     </row>
@@ -698,7 +692,7 @@
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Cross-check anything that looks wrong against the filing itself at sec.gov/edgar. Note that a single 10-K carries only TWO years of balance sheet data; the API aggregates across filings to reach five.</t>
+          <t>Cross-check anything that looks wrong against the filing itself at sec.gov/edgar. Interest Expense is already entered as a positive number, because it is a cost.</t>
         </is>
       </c>
     </row>
@@ -712,28 +706,28 @@
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>1. INTEREST EXPENSE is usually shown as a NEGATIVE number on financial websites (-163.4). Type it in as a POSITIVE number (163.4). It is a cost, and the template already treats it as one. If you leave it negative, Times Interest Earned comes out negative and nothing downstream makes sense.</t>
+          <t>1. Point every formula at the Financial Data sheet, not at a number you copied out of it. That is the whole exercise - see 'The one rule about formulas' above.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2. Your balance sheet total may be off by a few tenths. That is rounding in the published figures, not your mistake. Off by tens or hundreds IS your mistake.</t>
+          <t>2. Your balance sheet check row may be off by a few tenths. That is rounding in the published figures. Off by tens or hundreds means something is genuinely wrong - tell me.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Picking a company</t>
+          <t>About your company</t>
         </is>
       </c>
     </row>
     <row r="36" ht="56" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Pick a company you have heard of that makes or sells something physical. Avoid banks, insurers, and investment firms -- their balance sheets have no current assets subtotal and most of these ratios will not compute. Avoid companies that lost money in most of the five years; negative net income makes margins and returns hard to read.</t>
+          <t>Companies with a captive finance arm, and any bank or insurer, do not publish a current-assets subtotal, so the liquidity ratios cannot be computed for them. The tool refuses those up front, so whatever you were given works.</t>
         </is>
       </c>
     </row>
@@ -747,28 +741,28 @@
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   [ ]  The check row on the Financial Data sheet reads within about 1.0 of zero in all five years</t>
+          <t xml:space="preserve">   [ ]  Every green cell contains a formula, not a typed number</t>
         </is>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   [ ]  Interest Expense is shown positive (it is a cost; the app already flips the sign)</t>
+          <t xml:space="preserve">   [ ]  Every formula points back to the Financial Data sheet</t>
         </is>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   [ ]  Every green cell still contains a formula, not a pasted number</t>
+          <t xml:space="preserve">   [ ]  The DuPont check row on the Ratios sheet shows a difference of zero</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   [ ]  The DuPont check row on the Ratios sheet shows a difference of zero</t>
+          <t xml:space="preserve">   [ ]  The check row on the Financial Data sheet reads within about 1.0 of zero in all five years</t>
         </is>
       </c>
     </row>
@@ -1332,26 +1326,11 @@
           <t>Revenue (Net Sales)</t>
         </is>
       </c>
-      <c r="C10" s="16">
-        <f>'Financial Data'!C10/'Financial Data'!C$10</f>
-        <v/>
-      </c>
-      <c r="D10" s="16">
-        <f>'Financial Data'!D10/'Financial Data'!D$10</f>
-        <v/>
-      </c>
-      <c r="E10" s="16">
-        <f>'Financial Data'!E10/'Financial Data'!E$10</f>
-        <v/>
-      </c>
-      <c r="F10" s="16">
-        <f>'Financial Data'!F10/'Financial Data'!F$10</f>
-        <v/>
-      </c>
-      <c r="G10" s="16">
-        <f>'Financial Data'!G10/'Financial Data'!G$10</f>
-        <v/>
-      </c>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1359,26 +1338,11 @@
           <t>Cost of Revenue (COGS)</t>
         </is>
       </c>
-      <c r="C11" s="16">
-        <f>'Financial Data'!C11/'Financial Data'!C$10</f>
-        <v/>
-      </c>
-      <c r="D11" s="16">
-        <f>'Financial Data'!D11/'Financial Data'!D$10</f>
-        <v/>
-      </c>
-      <c r="E11" s="16">
-        <f>'Financial Data'!E11/'Financial Data'!E$10</f>
-        <v/>
-      </c>
-      <c r="F11" s="16">
-        <f>'Financial Data'!F11/'Financial Data'!F$10</f>
-        <v/>
-      </c>
-      <c r="G11" s="16">
-        <f>'Financial Data'!G11/'Financial Data'!G$10</f>
-        <v/>
-      </c>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1386,26 +1350,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C12" s="16">
-        <f>'Financial Data'!C12/'Financial Data'!C$10</f>
-        <v/>
-      </c>
-      <c r="D12" s="16">
-        <f>'Financial Data'!D12/'Financial Data'!D$10</f>
-        <v/>
-      </c>
-      <c r="E12" s="16">
-        <f>'Financial Data'!E12/'Financial Data'!E$10</f>
-        <v/>
-      </c>
-      <c r="F12" s="16">
-        <f>'Financial Data'!F12/'Financial Data'!F$10</f>
-        <v/>
-      </c>
-      <c r="G12" s="16">
-        <f>'Financial Data'!G12/'Financial Data'!G$10</f>
-        <v/>
-      </c>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1413,26 +1362,11 @@
           <t>Operating Expenses</t>
         </is>
       </c>
-      <c r="C13" s="16">
-        <f>'Financial Data'!C13/'Financial Data'!C$10</f>
-        <v/>
-      </c>
-      <c r="D13" s="16">
-        <f>'Financial Data'!D13/'Financial Data'!D$10</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>'Financial Data'!E13/'Financial Data'!E$10</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>'Financial Data'!F13/'Financial Data'!F$10</f>
-        <v/>
-      </c>
-      <c r="G13" s="16">
-        <f>'Financial Data'!G13/'Financial Data'!G$10</f>
-        <v/>
-      </c>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="16" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1440,26 +1374,11 @@
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
-      <c r="C14" s="16">
-        <f>'Financial Data'!C14/'Financial Data'!C$10</f>
-        <v/>
-      </c>
-      <c r="D14" s="16">
-        <f>'Financial Data'!D14/'Financial Data'!D$10</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>'Financial Data'!E14/'Financial Data'!E$10</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
-        <f>'Financial Data'!F14/'Financial Data'!F$10</f>
-        <v/>
-      </c>
-      <c r="G14" s="16">
-        <f>'Financial Data'!G14/'Financial Data'!G$10</f>
-        <v/>
-      </c>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="16" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1467,26 +1386,11 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="C15" s="16">
-        <f>'Financial Data'!C15/'Financial Data'!C$10</f>
-        <v/>
-      </c>
-      <c r="D15" s="16">
-        <f>'Financial Data'!D15/'Financial Data'!D$10</f>
-        <v/>
-      </c>
-      <c r="E15" s="16">
-        <f>'Financial Data'!E15/'Financial Data'!E$10</f>
-        <v/>
-      </c>
-      <c r="F15" s="16">
-        <f>'Financial Data'!F15/'Financial Data'!F$10</f>
-        <v/>
-      </c>
-      <c r="G15" s="16">
-        <f>'Financial Data'!G15/'Financial Data'!G$10</f>
-        <v/>
-      </c>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="16" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1494,26 +1398,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="C16" s="16">
-        <f>'Financial Data'!C16/'Financial Data'!C$10</f>
-        <v/>
-      </c>
-      <c r="D16" s="16">
-        <f>'Financial Data'!D16/'Financial Data'!D$10</f>
-        <v/>
-      </c>
-      <c r="E16" s="16">
-        <f>'Financial Data'!E16/'Financial Data'!E$10</f>
-        <v/>
-      </c>
-      <c r="F16" s="16">
-        <f>'Financial Data'!F16/'Financial Data'!F$10</f>
-        <v/>
-      </c>
-      <c r="G16" s="16">
-        <f>'Financial Data'!G16/'Financial Data'!G$10</f>
-        <v/>
-      </c>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1521,26 +1410,11 @@
           <t>Income Tax Expense</t>
         </is>
       </c>
-      <c r="C17" s="16">
-        <f>'Financial Data'!C17/'Financial Data'!C$10</f>
-        <v/>
-      </c>
-      <c r="D17" s="16">
-        <f>'Financial Data'!D17/'Financial Data'!D$10</f>
-        <v/>
-      </c>
-      <c r="E17" s="16">
-        <f>'Financial Data'!E17/'Financial Data'!E$10</f>
-        <v/>
-      </c>
-      <c r="F17" s="16">
-        <f>'Financial Data'!F17/'Financial Data'!F$10</f>
-        <v/>
-      </c>
-      <c r="G17" s="16">
-        <f>'Financial Data'!G17/'Financial Data'!G$10</f>
-        <v/>
-      </c>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1548,26 +1422,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="C18" s="16">
-        <f>'Financial Data'!C18/'Financial Data'!C$10</f>
-        <v/>
-      </c>
-      <c r="D18" s="16">
-        <f>'Financial Data'!D18/'Financial Data'!D$10</f>
-        <v/>
-      </c>
-      <c r="E18" s="16">
-        <f>'Financial Data'!E18/'Financial Data'!E$10</f>
-        <v/>
-      </c>
-      <c r="F18" s="16">
-        <f>'Financial Data'!F18/'Financial Data'!F$10</f>
-        <v/>
-      </c>
-      <c r="G18" s="16">
-        <f>'Financial Data'!G18/'Financial Data'!G$10</f>
-        <v/>
-      </c>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="16" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
@@ -1587,26 +1446,11 @@
           <t>Cash &amp; Short-Term Investments</t>
         </is>
       </c>
-      <c r="C21" s="16">
-        <f>'Financial Data'!C21/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D21" s="16">
-        <f>'Financial Data'!D21/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E21" s="16">
-        <f>'Financial Data'!E21/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F21" s="16">
-        <f>'Financial Data'!F21/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G21" s="16">
-        <f>'Financial Data'!G21/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="16" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1614,26 +1458,11 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="C22" s="16">
-        <f>'Financial Data'!C22/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D22" s="16">
-        <f>'Financial Data'!D22/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E22" s="16">
-        <f>'Financial Data'!E22/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F22" s="16">
-        <f>'Financial Data'!F22/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G22" s="16">
-        <f>'Financial Data'!G22/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="16" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -1641,26 +1470,11 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C23" s="16">
-        <f>'Financial Data'!C23/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D23" s="16">
-        <f>'Financial Data'!D23/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E23" s="16">
-        <f>'Financial Data'!E23/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F23" s="16">
-        <f>'Financial Data'!F23/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G23" s="16">
-        <f>'Financial Data'!G23/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="16" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1668,26 +1482,11 @@
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="C24" s="16">
-        <f>'Financial Data'!C24/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D24" s="16">
-        <f>'Financial Data'!D24/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E24" s="16">
-        <f>'Financial Data'!E24/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F24" s="16">
-        <f>'Financial Data'!F24/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G24" s="16">
-        <f>'Financial Data'!G24/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -1695,26 +1494,11 @@
           <t>Total Current Assets</t>
         </is>
       </c>
-      <c r="C25" s="16">
-        <f>'Financial Data'!C25/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D25" s="16">
-        <f>'Financial Data'!D25/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E25" s="16">
-        <f>'Financial Data'!E25/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F25" s="16">
-        <f>'Financial Data'!F25/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G25" s="16">
-        <f>'Financial Data'!G25/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="16" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1722,26 +1506,11 @@
           <t>Property, Plant &amp; Equipment (net)</t>
         </is>
       </c>
-      <c r="C26" s="16">
-        <f>'Financial Data'!C26/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D26" s="16">
-        <f>'Financial Data'!D26/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E26" s="16">
-        <f>'Financial Data'!E26/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F26" s="16">
-        <f>'Financial Data'!F26/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G26" s="16">
-        <f>'Financial Data'!G26/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="16" t="n"/>
+      <c r="G26" s="16" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1749,26 +1518,11 @@
           <t>Goodwill &amp; Intangible Assets</t>
         </is>
       </c>
-      <c r="C27" s="16">
-        <f>'Financial Data'!C27/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D27" s="16">
-        <f>'Financial Data'!D27/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E27" s="16">
-        <f>'Financial Data'!E27/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F27" s="16">
-        <f>'Financial Data'!F27/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G27" s="16">
-        <f>'Financial Data'!G27/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="16" t="n"/>
+      <c r="G27" s="16" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1776,26 +1530,11 @@
           <t>Other Long-Term Assets</t>
         </is>
       </c>
-      <c r="C28" s="16">
-        <f>'Financial Data'!C28/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D28" s="16">
-        <f>'Financial Data'!D28/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E28" s="16">
-        <f>'Financial Data'!E28/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F28" s="16">
-        <f>'Financial Data'!F28/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G28" s="16">
-        <f>'Financial Data'!G28/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="16" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -1803,26 +1542,11 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="C29" s="16">
-        <f>'Financial Data'!C29/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D29" s="16">
-        <f>'Financial Data'!D29/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E29" s="16">
-        <f>'Financial Data'!E29/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F29" s="16">
-        <f>'Financial Data'!F29/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G29" s="16">
-        <f>'Financial Data'!G29/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" s="16" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
@@ -1837,26 +1561,11 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="C32" s="16">
-        <f>'Financial Data'!C32/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D32" s="16">
-        <f>'Financial Data'!D32/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E32" s="16">
-        <f>'Financial Data'!E32/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F32" s="16">
-        <f>'Financial Data'!F32/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G32" s="16">
-        <f>'Financial Data'!G32/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="16" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -1864,26 +1573,11 @@
           <t>Short-Term Debt &amp; Current Portion of LTD</t>
         </is>
       </c>
-      <c r="C33" s="16">
-        <f>'Financial Data'!C33/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D33" s="16">
-        <f>'Financial Data'!D33/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E33" s="16">
-        <f>'Financial Data'!E33/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F33" s="16">
-        <f>'Financial Data'!F33/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G33" s="16">
-        <f>'Financial Data'!G33/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="16" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -1891,26 +1585,11 @@
           <t>Other Current Liabilities</t>
         </is>
       </c>
-      <c r="C34" s="16">
-        <f>'Financial Data'!C34/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D34" s="16">
-        <f>'Financial Data'!D34/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E34" s="16">
-        <f>'Financial Data'!E34/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F34" s="16">
-        <f>'Financial Data'!F34/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G34" s="16">
-        <f>'Financial Data'!G34/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="n"/>
+      <c r="F34" s="16" t="n"/>
+      <c r="G34" s="16" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -1918,26 +1597,11 @@
           <t>Total Current Liabilities</t>
         </is>
       </c>
-      <c r="C35" s="16">
-        <f>'Financial Data'!C35/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D35" s="16">
-        <f>'Financial Data'!D35/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E35" s="16">
-        <f>'Financial Data'!E35/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F35" s="16">
-        <f>'Financial Data'!F35/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G35" s="16">
-        <f>'Financial Data'!G35/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
+      <c r="G35" s="16" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -1945,26 +1609,11 @@
           <t>Long-Term Debt</t>
         </is>
       </c>
-      <c r="C36" s="16">
-        <f>'Financial Data'!C36/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D36" s="16">
-        <f>'Financial Data'!D36/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E36" s="16">
-        <f>'Financial Data'!E36/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F36" s="16">
-        <f>'Financial Data'!F36/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G36" s="16">
-        <f>'Financial Data'!G36/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
+      <c r="G36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -1972,26 +1621,11 @@
           <t>Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="C37" s="16">
-        <f>'Financial Data'!C37/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D37" s="16">
-        <f>'Financial Data'!D37/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E37" s="16">
-        <f>'Financial Data'!E37/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F37" s="16">
-        <f>'Financial Data'!F37/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G37" s="16">
-        <f>'Financial Data'!G37/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="16" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -1999,26 +1633,11 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="C38" s="16">
-        <f>'Financial Data'!C38/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D38" s="16">
-        <f>'Financial Data'!D38/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E38" s="16">
-        <f>'Financial Data'!E38/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F38" s="16">
-        <f>'Financial Data'!F38/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G38" s="16">
-        <f>'Financial Data'!G38/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
+      <c r="G38" s="16" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -2026,26 +1645,11 @@
           <t>Total Shareholders' Equity</t>
         </is>
       </c>
-      <c r="C39" s="16">
-        <f>'Financial Data'!C39/'Financial Data'!C$29</f>
-        <v/>
-      </c>
-      <c r="D39" s="16">
-        <f>'Financial Data'!D39/'Financial Data'!D$29</f>
-        <v/>
-      </c>
-      <c r="E39" s="16">
-        <f>'Financial Data'!E39/'Financial Data'!E$29</f>
-        <v/>
-      </c>
-      <c r="F39" s="16">
-        <f>'Financial Data'!F39/'Financial Data'!F$29</f>
-        <v/>
-      </c>
-      <c r="G39" s="16">
-        <f>'Financial Data'!G39/'Financial Data'!G$29</f>
-        <v/>
-      </c>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="16" t="n"/>
+      <c r="G39" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2144,22 +1748,10 @@
         </is>
       </c>
       <c r="C6" s="20" t="n"/>
-      <c r="D6" s="16">
-        <f>('Financial Data'!D10-'Financial Data'!C10)/'Financial Data'!C10</f>
-        <v/>
-      </c>
-      <c r="E6" s="16">
-        <f>('Financial Data'!E10-'Financial Data'!D10)/'Financial Data'!D10</f>
-        <v/>
-      </c>
-      <c r="F6" s="16">
-        <f>('Financial Data'!F10-'Financial Data'!E10)/'Financial Data'!E10</f>
-        <v/>
-      </c>
-      <c r="G6" s="16">
-        <f>('Financial Data'!G10-'Financial Data'!F10)/'Financial Data'!F10</f>
-        <v/>
-      </c>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="16" t="n"/>
       <c r="I6" s="11" t="inlineStr">
         <is>
           <t>(This year - Last year) / Last year. There is no percent change for your earliest year because there is nothing before it.</t>
@@ -2173,22 +1765,10 @@
         </is>
       </c>
       <c r="C7" s="20" t="n"/>
-      <c r="D7" s="16">
-        <f>('Financial Data'!D11-'Financial Data'!C11)/'Financial Data'!C11</f>
-        <v/>
-      </c>
-      <c r="E7" s="16">
-        <f>('Financial Data'!E11-'Financial Data'!D11)/'Financial Data'!D11</f>
-        <v/>
-      </c>
-      <c r="F7" s="16">
-        <f>('Financial Data'!F11-'Financial Data'!E11)/'Financial Data'!E11</f>
-        <v/>
-      </c>
-      <c r="G7" s="16">
-        <f>('Financial Data'!G11-'Financial Data'!F11)/'Financial Data'!F11</f>
-        <v/>
-      </c>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2197,22 +1777,10 @@
         </is>
       </c>
       <c r="C8" s="20" t="n"/>
-      <c r="D8" s="16">
-        <f>('Financial Data'!D12-'Financial Data'!C12)/'Financial Data'!C12</f>
-        <v/>
-      </c>
-      <c r="E8" s="16">
-        <f>('Financial Data'!E12-'Financial Data'!D12)/'Financial Data'!D12</f>
-        <v/>
-      </c>
-      <c r="F8" s="16">
-        <f>('Financial Data'!F12-'Financial Data'!E12)/'Financial Data'!E12</f>
-        <v/>
-      </c>
-      <c r="G8" s="16">
-        <f>('Financial Data'!G12-'Financial Data'!F12)/'Financial Data'!F12</f>
-        <v/>
-      </c>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -2221,22 +1789,10 @@
         </is>
       </c>
       <c r="C9" s="20" t="n"/>
-      <c r="D9" s="16">
-        <f>('Financial Data'!D14-'Financial Data'!C14)/'Financial Data'!C14</f>
-        <v/>
-      </c>
-      <c r="E9" s="16">
-        <f>('Financial Data'!E14-'Financial Data'!D14)/'Financial Data'!D14</f>
-        <v/>
-      </c>
-      <c r="F9" s="16">
-        <f>('Financial Data'!F14-'Financial Data'!E14)/'Financial Data'!E14</f>
-        <v/>
-      </c>
-      <c r="G9" s="16">
-        <f>('Financial Data'!G14-'Financial Data'!F14)/'Financial Data'!F14</f>
-        <v/>
-      </c>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -2245,22 +1801,10 @@
         </is>
       </c>
       <c r="C10" s="20" t="n"/>
-      <c r="D10" s="16">
-        <f>('Financial Data'!D18-'Financial Data'!C18)/'Financial Data'!C18</f>
-        <v/>
-      </c>
-      <c r="E10" s="16">
-        <f>('Financial Data'!E18-'Financial Data'!D18)/'Financial Data'!D18</f>
-        <v/>
-      </c>
-      <c r="F10" s="16">
-        <f>('Financial Data'!F18-'Financial Data'!E18)/'Financial Data'!E18</f>
-        <v/>
-      </c>
-      <c r="G10" s="16">
-        <f>('Financial Data'!G18-'Financial Data'!F18)/'Financial Data'!F18</f>
-        <v/>
-      </c>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -2269,22 +1813,10 @@
         </is>
       </c>
       <c r="C11" s="20" t="n"/>
-      <c r="D11" s="16">
-        <f>('Financial Data'!D23-'Financial Data'!C23)/'Financial Data'!C23</f>
-        <v/>
-      </c>
-      <c r="E11" s="16">
-        <f>('Financial Data'!E23-'Financial Data'!D23)/'Financial Data'!D23</f>
-        <v/>
-      </c>
-      <c r="F11" s="16">
-        <f>('Financial Data'!F23-'Financial Data'!E23)/'Financial Data'!E23</f>
-        <v/>
-      </c>
-      <c r="G11" s="16">
-        <f>('Financial Data'!G23-'Financial Data'!F23)/'Financial Data'!F23</f>
-        <v/>
-      </c>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2293,22 +1825,10 @@
         </is>
       </c>
       <c r="C12" s="20" t="n"/>
-      <c r="D12" s="16">
-        <f>('Financial Data'!D25-'Financial Data'!C25)/'Financial Data'!C25</f>
-        <v/>
-      </c>
-      <c r="E12" s="16">
-        <f>('Financial Data'!E25-'Financial Data'!D25)/'Financial Data'!D25</f>
-        <v/>
-      </c>
-      <c r="F12" s="16">
-        <f>('Financial Data'!F25-'Financial Data'!E25)/'Financial Data'!E25</f>
-        <v/>
-      </c>
-      <c r="G12" s="16">
-        <f>('Financial Data'!G25-'Financial Data'!F25)/'Financial Data'!F25</f>
-        <v/>
-      </c>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -2317,22 +1837,10 @@
         </is>
       </c>
       <c r="C13" s="20" t="n"/>
-      <c r="D13" s="16">
-        <f>('Financial Data'!D29-'Financial Data'!C29)/'Financial Data'!C29</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>('Financial Data'!E29-'Financial Data'!D29)/'Financial Data'!D29</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>('Financial Data'!F29-'Financial Data'!E29)/'Financial Data'!E29</f>
-        <v/>
-      </c>
-      <c r="G13" s="16">
-        <f>('Financial Data'!G29-'Financial Data'!F29)/'Financial Data'!F29</f>
-        <v/>
-      </c>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="16" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -2341,22 +1849,10 @@
         </is>
       </c>
       <c r="C14" s="20" t="n"/>
-      <c r="D14" s="16">
-        <f>('Financial Data'!D38-'Financial Data'!C38)/'Financial Data'!C38</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>('Financial Data'!E38-'Financial Data'!D38)/'Financial Data'!D38</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
-        <f>('Financial Data'!F38-'Financial Data'!E38)/'Financial Data'!E38</f>
-        <v/>
-      </c>
-      <c r="G14" s="16">
-        <f>('Financial Data'!G38-'Financial Data'!F38)/'Financial Data'!F38</f>
-        <v/>
-      </c>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="16" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -2365,22 +1861,10 @@
         </is>
       </c>
       <c r="C15" s="20" t="n"/>
-      <c r="D15" s="16">
-        <f>('Financial Data'!D39-'Financial Data'!C39)/'Financial Data'!C39</f>
-        <v/>
-      </c>
-      <c r="E15" s="16">
-        <f>('Financial Data'!E39-'Financial Data'!D39)/'Financial Data'!D39</f>
-        <v/>
-      </c>
-      <c r="F15" s="16">
-        <f>('Financial Data'!F39-'Financial Data'!E39)/'Financial Data'!E39</f>
-        <v/>
-      </c>
-      <c r="G15" s="16">
-        <f>('Financial Data'!G39-'Financial Data'!F39)/'Financial Data'!F39</f>
-        <v/>
-      </c>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
@@ -2430,26 +1914,11 @@
           <t>Revenue (Net Sales)</t>
         </is>
       </c>
-      <c r="C20" s="21">
-        <f>'Financial Data'!C10/'Financial Data'!$C$10*100</f>
-        <v/>
-      </c>
-      <c r="D20" s="21">
-        <f>'Financial Data'!D10/'Financial Data'!$C$10*100</f>
-        <v/>
-      </c>
-      <c r="E20" s="21">
-        <f>'Financial Data'!E10/'Financial Data'!$C$10*100</f>
-        <v/>
-      </c>
-      <c r="F20" s="21">
-        <f>'Financial Data'!F10/'Financial Data'!$C$10*100</f>
-        <v/>
-      </c>
-      <c r="G20" s="21">
-        <f>'Financial Data'!G10/'Financial Data'!$C$10*100</f>
-        <v/>
-      </c>
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="21" t="n"/>
+      <c r="G20" s="21" t="n"/>
       <c r="I20" s="11" t="inlineStr">
         <is>
           <t>Year N / earliest year x 100. Your earliest year will come out to exactly 100.0 - that is the check that you did it right. Lock the base year column with $.</t>
@@ -2462,26 +1931,11 @@
           <t>Cost of Revenue (COGS)</t>
         </is>
       </c>
-      <c r="C21" s="21">
-        <f>'Financial Data'!C11/'Financial Data'!$C$11*100</f>
-        <v/>
-      </c>
-      <c r="D21" s="21">
-        <f>'Financial Data'!D11/'Financial Data'!$C$11*100</f>
-        <v/>
-      </c>
-      <c r="E21" s="21">
-        <f>'Financial Data'!E11/'Financial Data'!$C$11*100</f>
-        <v/>
-      </c>
-      <c r="F21" s="21">
-        <f>'Financial Data'!F11/'Financial Data'!$C$11*100</f>
-        <v/>
-      </c>
-      <c r="G21" s="21">
-        <f>'Financial Data'!G11/'Financial Data'!$C$11*100</f>
-        <v/>
-      </c>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="21" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -2489,26 +1943,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C22" s="21">
-        <f>'Financial Data'!C12/'Financial Data'!$C$12*100</f>
-        <v/>
-      </c>
-      <c r="D22" s="21">
-        <f>'Financial Data'!D12/'Financial Data'!$C$12*100</f>
-        <v/>
-      </c>
-      <c r="E22" s="21">
-        <f>'Financial Data'!E12/'Financial Data'!$C$12*100</f>
-        <v/>
-      </c>
-      <c r="F22" s="21">
-        <f>'Financial Data'!F12/'Financial Data'!$C$12*100</f>
-        <v/>
-      </c>
-      <c r="G22" s="21">
-        <f>'Financial Data'!G12/'Financial Data'!$C$12*100</f>
-        <v/>
-      </c>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="21" t="n"/>
+      <c r="G22" s="21" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -2516,26 +1955,11 @@
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
-      <c r="C23" s="21">
-        <f>'Financial Data'!C14/'Financial Data'!$C$14*100</f>
-        <v/>
-      </c>
-      <c r="D23" s="21">
-        <f>'Financial Data'!D14/'Financial Data'!$C$14*100</f>
-        <v/>
-      </c>
-      <c r="E23" s="21">
-        <f>'Financial Data'!E14/'Financial Data'!$C$14*100</f>
-        <v/>
-      </c>
-      <c r="F23" s="21">
-        <f>'Financial Data'!F14/'Financial Data'!$C$14*100</f>
-        <v/>
-      </c>
-      <c r="G23" s="21">
-        <f>'Financial Data'!G14/'Financial Data'!$C$14*100</f>
-        <v/>
-      </c>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="21" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -2543,26 +1967,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="C24" s="21">
-        <f>'Financial Data'!C18/'Financial Data'!$C$18*100</f>
-        <v/>
-      </c>
-      <c r="D24" s="21">
-        <f>'Financial Data'!D18/'Financial Data'!$C$18*100</f>
-        <v/>
-      </c>
-      <c r="E24" s="21">
-        <f>'Financial Data'!E18/'Financial Data'!$C$18*100</f>
-        <v/>
-      </c>
-      <c r="F24" s="21">
-        <f>'Financial Data'!F18/'Financial Data'!$C$18*100</f>
-        <v/>
-      </c>
-      <c r="G24" s="21">
-        <f>'Financial Data'!G18/'Financial Data'!$C$18*100</f>
-        <v/>
-      </c>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="21" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -2570,26 +1979,11 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C25" s="21">
-        <f>'Financial Data'!C23/'Financial Data'!$C$23*100</f>
-        <v/>
-      </c>
-      <c r="D25" s="21">
-        <f>'Financial Data'!D23/'Financial Data'!$C$23*100</f>
-        <v/>
-      </c>
-      <c r="E25" s="21">
-        <f>'Financial Data'!E23/'Financial Data'!$C$23*100</f>
-        <v/>
-      </c>
-      <c r="F25" s="21">
-        <f>'Financial Data'!F23/'Financial Data'!$C$23*100</f>
-        <v/>
-      </c>
-      <c r="G25" s="21">
-        <f>'Financial Data'!G23/'Financial Data'!$C$23*100</f>
-        <v/>
-      </c>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="21" t="n"/>
+      <c r="G25" s="21" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -2597,26 +1991,11 @@
           <t>Total Current Assets</t>
         </is>
       </c>
-      <c r="C26" s="21">
-        <f>'Financial Data'!C25/'Financial Data'!$C$25*100</f>
-        <v/>
-      </c>
-      <c r="D26" s="21">
-        <f>'Financial Data'!D25/'Financial Data'!$C$25*100</f>
-        <v/>
-      </c>
-      <c r="E26" s="21">
-        <f>'Financial Data'!E25/'Financial Data'!$C$25*100</f>
-        <v/>
-      </c>
-      <c r="F26" s="21">
-        <f>'Financial Data'!F25/'Financial Data'!$C$25*100</f>
-        <v/>
-      </c>
-      <c r="G26" s="21">
-        <f>'Financial Data'!G25/'Financial Data'!$C$25*100</f>
-        <v/>
-      </c>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="21" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -2624,26 +2003,11 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="C27" s="21">
-        <f>'Financial Data'!C29/'Financial Data'!$C$29*100</f>
-        <v/>
-      </c>
-      <c r="D27" s="21">
-        <f>'Financial Data'!D29/'Financial Data'!$C$29*100</f>
-        <v/>
-      </c>
-      <c r="E27" s="21">
-        <f>'Financial Data'!E29/'Financial Data'!$C$29*100</f>
-        <v/>
-      </c>
-      <c r="F27" s="21">
-        <f>'Financial Data'!F29/'Financial Data'!$C$29*100</f>
-        <v/>
-      </c>
-      <c r="G27" s="21">
-        <f>'Financial Data'!G29/'Financial Data'!$C$29*100</f>
-        <v/>
-      </c>
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="21" t="n"/>
+      <c r="E27" s="21" t="n"/>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="21" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -2651,26 +2015,11 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="C28" s="21">
-        <f>'Financial Data'!C38/'Financial Data'!$C$38*100</f>
-        <v/>
-      </c>
-      <c r="D28" s="21">
-        <f>'Financial Data'!D38/'Financial Data'!$C$38*100</f>
-        <v/>
-      </c>
-      <c r="E28" s="21">
-        <f>'Financial Data'!E38/'Financial Data'!$C$38*100</f>
-        <v/>
-      </c>
-      <c r="F28" s="21">
-        <f>'Financial Data'!F38/'Financial Data'!$C$38*100</f>
-        <v/>
-      </c>
-      <c r="G28" s="21">
-        <f>'Financial Data'!G38/'Financial Data'!$C$38*100</f>
-        <v/>
-      </c>
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="21" t="n"/>
+      <c r="E28" s="21" t="n"/>
+      <c r="F28" s="21" t="n"/>
+      <c r="G28" s="21" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -2678,26 +2027,11 @@
           <t>Total Shareholders' Equity</t>
         </is>
       </c>
-      <c r="C29" s="21">
-        <f>'Financial Data'!C39/'Financial Data'!$C$39*100</f>
-        <v/>
-      </c>
-      <c r="D29" s="21">
-        <f>'Financial Data'!D39/'Financial Data'!$C$39*100</f>
-        <v/>
-      </c>
-      <c r="E29" s="21">
-        <f>'Financial Data'!E39/'Financial Data'!$C$39*100</f>
-        <v/>
-      </c>
-      <c r="F29" s="21">
-        <f>'Financial Data'!F39/'Financial Data'!$C$39*100</f>
-        <v/>
-      </c>
-      <c r="G29" s="21">
-        <f>'Financial Data'!G39/'Financial Data'!$C$39*100</f>
-        <v/>
-      </c>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="21" t="n"/>
+      <c r="F29" s="21" t="n"/>
+      <c r="G29" s="21" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2786,26 +2120,11 @@
           <t>Current Ratio</t>
         </is>
       </c>
-      <c r="C10" s="22">
-        <f>'Financial Data'!C25/'Financial Data'!C35</f>
-        <v/>
-      </c>
-      <c r="D10" s="22">
-        <f>'Financial Data'!D25/'Financial Data'!D35</f>
-        <v/>
-      </c>
-      <c r="E10" s="22">
-        <f>'Financial Data'!E25/'Financial Data'!E35</f>
-        <v/>
-      </c>
-      <c r="F10" s="22">
-        <f>'Financial Data'!F25/'Financial Data'!F35</f>
-        <v/>
-      </c>
-      <c r="G10" s="22">
-        <f>'Financial Data'!G25/'Financial Data'!G35</f>
-        <v/>
-      </c>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
       <c r="I10" s="23" t="inlineStr">
         <is>
           <t>Total Current Assets / Total Current Liabilities</t>
@@ -2818,26 +2137,11 @@
           <t>Quick Ratio</t>
         </is>
       </c>
-      <c r="C11" s="22">
-        <f>('Financial Data'!C25-'Financial Data'!C23)/'Financial Data'!C35</f>
-        <v/>
-      </c>
-      <c r="D11" s="22">
-        <f>('Financial Data'!D25-'Financial Data'!D23)/'Financial Data'!D35</f>
-        <v/>
-      </c>
-      <c r="E11" s="22">
-        <f>('Financial Data'!E25-'Financial Data'!E23)/'Financial Data'!E35</f>
-        <v/>
-      </c>
-      <c r="F11" s="22">
-        <f>('Financial Data'!F25-'Financial Data'!F23)/'Financial Data'!F35</f>
-        <v/>
-      </c>
-      <c r="G11" s="22">
-        <f>('Financial Data'!G25-'Financial Data'!G23)/'Financial Data'!G35</f>
-        <v/>
-      </c>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
       <c r="I11" s="23" t="inlineStr">
         <is>
           <t>(Total Current Assets - Inventory) / Total Current Liabilities</t>
@@ -2850,26 +2154,11 @@
           <t>Cash Ratio</t>
         </is>
       </c>
-      <c r="C12" s="22">
-        <f>'Financial Data'!C21/'Financial Data'!C35</f>
-        <v/>
-      </c>
-      <c r="D12" s="22">
-        <f>'Financial Data'!D21/'Financial Data'!D35</f>
-        <v/>
-      </c>
-      <c r="E12" s="22">
-        <f>'Financial Data'!E21/'Financial Data'!E35</f>
-        <v/>
-      </c>
-      <c r="F12" s="22">
-        <f>'Financial Data'!F21/'Financial Data'!F35</f>
-        <v/>
-      </c>
-      <c r="G12" s="22">
-        <f>'Financial Data'!G21/'Financial Data'!G35</f>
-        <v/>
-      </c>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
       <c r="I12" s="23" t="inlineStr">
         <is>
           <t>Cash &amp; Short-Term Investments / Total Current Liabilities</t>
@@ -2889,26 +2178,11 @@
           <t>Debt Ratio</t>
         </is>
       </c>
-      <c r="C15" s="16">
-        <f>'Financial Data'!C38/'Financial Data'!C29</f>
-        <v/>
-      </c>
-      <c r="D15" s="16">
-        <f>'Financial Data'!D38/'Financial Data'!D29</f>
-        <v/>
-      </c>
-      <c r="E15" s="16">
-        <f>'Financial Data'!E38/'Financial Data'!E29</f>
-        <v/>
-      </c>
-      <c r="F15" s="16">
-        <f>'Financial Data'!F38/'Financial Data'!F29</f>
-        <v/>
-      </c>
-      <c r="G15" s="16">
-        <f>'Financial Data'!G38/'Financial Data'!G29</f>
-        <v/>
-      </c>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="16" t="n"/>
       <c r="I15" s="23" t="inlineStr">
         <is>
           <t>Total Liabilities / Total Assets</t>
@@ -2921,26 +2195,11 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="C16" s="22">
-        <f>'Financial Data'!C38/'Financial Data'!C39</f>
-        <v/>
-      </c>
-      <c r="D16" s="22">
-        <f>'Financial Data'!D38/'Financial Data'!D39</f>
-        <v/>
-      </c>
-      <c r="E16" s="22">
-        <f>'Financial Data'!E38/'Financial Data'!E39</f>
-        <v/>
-      </c>
-      <c r="F16" s="22">
-        <f>'Financial Data'!F38/'Financial Data'!F39</f>
-        <v/>
-      </c>
-      <c r="G16" s="22">
-        <f>'Financial Data'!G38/'Financial Data'!G39</f>
-        <v/>
-      </c>
+      <c r="C16" s="22" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="22" t="n"/>
+      <c r="G16" s="22" t="n"/>
       <c r="I16" s="23" t="inlineStr">
         <is>
           <t>Total Liabilities / Total Shareholders' Equity</t>
@@ -2953,26 +2212,11 @@
           <t>Equity Multiplier</t>
         </is>
       </c>
-      <c r="C17" s="22">
-        <f>'Financial Data'!C29/'Financial Data'!C39</f>
-        <v/>
-      </c>
-      <c r="D17" s="22">
-        <f>'Financial Data'!D29/'Financial Data'!D39</f>
-        <v/>
-      </c>
-      <c r="E17" s="22">
-        <f>'Financial Data'!E29/'Financial Data'!E39</f>
-        <v/>
-      </c>
-      <c r="F17" s="22">
-        <f>'Financial Data'!F29/'Financial Data'!F39</f>
-        <v/>
-      </c>
-      <c r="G17" s="22">
-        <f>'Financial Data'!G29/'Financial Data'!G39</f>
-        <v/>
-      </c>
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
       <c r="I17" s="23" t="inlineStr">
         <is>
           <t>Total Assets / Total Shareholders' Equity</t>
@@ -2985,26 +2229,11 @@
           <t>Times Interest Earned</t>
         </is>
       </c>
-      <c r="C18" s="22">
-        <f>'Financial Data'!C14/'Financial Data'!C15</f>
-        <v/>
-      </c>
-      <c r="D18" s="22">
-        <f>'Financial Data'!D14/'Financial Data'!D15</f>
-        <v/>
-      </c>
-      <c r="E18" s="22">
-        <f>'Financial Data'!E14/'Financial Data'!E15</f>
-        <v/>
-      </c>
-      <c r="F18" s="22">
-        <f>'Financial Data'!F14/'Financial Data'!F15</f>
-        <v/>
-      </c>
-      <c r="G18" s="22">
-        <f>'Financial Data'!G14/'Financial Data'!G15</f>
-        <v/>
-      </c>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
       <c r="I18" s="23" t="inlineStr">
         <is>
           <t>Operating Income (EBIT) / Interest Expense</t>
@@ -3024,26 +2253,11 @@
           <t>Gross Margin</t>
         </is>
       </c>
-      <c r="C21" s="16">
-        <f>'Financial Data'!C12/'Financial Data'!C10</f>
-        <v/>
-      </c>
-      <c r="D21" s="16">
-        <f>'Financial Data'!D12/'Financial Data'!D10</f>
-        <v/>
-      </c>
-      <c r="E21" s="16">
-        <f>'Financial Data'!E12/'Financial Data'!E10</f>
-        <v/>
-      </c>
-      <c r="F21" s="16">
-        <f>'Financial Data'!F12/'Financial Data'!F10</f>
-        <v/>
-      </c>
-      <c r="G21" s="16">
-        <f>'Financial Data'!G12/'Financial Data'!G10</f>
-        <v/>
-      </c>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="16" t="n"/>
       <c r="I21" s="23" t="inlineStr">
         <is>
           <t>Gross Profit / Revenue</t>
@@ -3056,26 +2270,11 @@
           <t>Operating Margin</t>
         </is>
       </c>
-      <c r="C22" s="16">
-        <f>'Financial Data'!C14/'Financial Data'!C10</f>
-        <v/>
-      </c>
-      <c r="D22" s="16">
-        <f>'Financial Data'!D14/'Financial Data'!D10</f>
-        <v/>
-      </c>
-      <c r="E22" s="16">
-        <f>'Financial Data'!E14/'Financial Data'!E10</f>
-        <v/>
-      </c>
-      <c r="F22" s="16">
-        <f>'Financial Data'!F14/'Financial Data'!F10</f>
-        <v/>
-      </c>
-      <c r="G22" s="16">
-        <f>'Financial Data'!G14/'Financial Data'!G10</f>
-        <v/>
-      </c>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="16" t="n"/>
       <c r="I22" s="23" t="inlineStr">
         <is>
           <t>Operating Income (EBIT) / Revenue</t>
@@ -3088,26 +2287,11 @@
           <t>Net Profit Margin</t>
         </is>
       </c>
-      <c r="C23" s="16">
-        <f>'Financial Data'!C18/'Financial Data'!C10</f>
-        <v/>
-      </c>
-      <c r="D23" s="16">
-        <f>'Financial Data'!D18/'Financial Data'!D10</f>
-        <v/>
-      </c>
-      <c r="E23" s="16">
-        <f>'Financial Data'!E18/'Financial Data'!E10</f>
-        <v/>
-      </c>
-      <c r="F23" s="16">
-        <f>'Financial Data'!F18/'Financial Data'!F10</f>
-        <v/>
-      </c>
-      <c r="G23" s="16">
-        <f>'Financial Data'!G18/'Financial Data'!G10</f>
-        <v/>
-      </c>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="16" t="n"/>
       <c r="I23" s="23" t="inlineStr">
         <is>
           <t>Net Income / Revenue</t>
@@ -3120,26 +2304,11 @@
           <t>Return on Assets (ROA)</t>
         </is>
       </c>
-      <c r="C24" s="16">
-        <f>'Financial Data'!C18/'Financial Data'!C29</f>
-        <v/>
-      </c>
-      <c r="D24" s="16">
-        <f>'Financial Data'!D18/'Financial Data'!D29</f>
-        <v/>
-      </c>
-      <c r="E24" s="16">
-        <f>'Financial Data'!E18/'Financial Data'!E29</f>
-        <v/>
-      </c>
-      <c r="F24" s="16">
-        <f>'Financial Data'!F18/'Financial Data'!F29</f>
-        <v/>
-      </c>
-      <c r="G24" s="16">
-        <f>'Financial Data'!G18/'Financial Data'!G29</f>
-        <v/>
-      </c>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
       <c r="I24" s="23" t="inlineStr">
         <is>
           <t>Net Income / Total Assets</t>
@@ -3152,26 +2321,11 @@
           <t>Return on Equity (ROE)</t>
         </is>
       </c>
-      <c r="C25" s="16">
-        <f>'Financial Data'!C18/'Financial Data'!C39</f>
-        <v/>
-      </c>
-      <c r="D25" s="16">
-        <f>'Financial Data'!D18/'Financial Data'!D39</f>
-        <v/>
-      </c>
-      <c r="E25" s="16">
-        <f>'Financial Data'!E18/'Financial Data'!E39</f>
-        <v/>
-      </c>
-      <c r="F25" s="16">
-        <f>'Financial Data'!F18/'Financial Data'!F39</f>
-        <v/>
-      </c>
-      <c r="G25" s="16">
-        <f>'Financial Data'!G18/'Financial Data'!G39</f>
-        <v/>
-      </c>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="16" t="n"/>
       <c r="I25" s="23" t="inlineStr">
         <is>
           <t>Net Income / Total Shareholders' Equity</t>
@@ -3191,26 +2345,11 @@
           <t>Inventory Turnover</t>
         </is>
       </c>
-      <c r="C28" s="22">
-        <f>'Financial Data'!C11/'Financial Data'!C23</f>
-        <v/>
-      </c>
-      <c r="D28" s="22">
-        <f>'Financial Data'!D11/'Financial Data'!D23</f>
-        <v/>
-      </c>
-      <c r="E28" s="22">
-        <f>'Financial Data'!E11/'Financial Data'!E23</f>
-        <v/>
-      </c>
-      <c r="F28" s="22">
-        <f>'Financial Data'!F11/'Financial Data'!F23</f>
-        <v/>
-      </c>
-      <c r="G28" s="22">
-        <f>'Financial Data'!G11/'Financial Data'!G23</f>
-        <v/>
-      </c>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="22" t="n"/>
       <c r="I28" s="23" t="inlineStr">
         <is>
           <t>Cost of Revenue (COGS) / Inventory</t>
@@ -3223,26 +2362,11 @@
           <t>Total Asset Turnover</t>
         </is>
       </c>
-      <c r="C29" s="22">
-        <f>'Financial Data'!C10/'Financial Data'!C29</f>
-        <v/>
-      </c>
-      <c r="D29" s="22">
-        <f>'Financial Data'!D10/'Financial Data'!D29</f>
-        <v/>
-      </c>
-      <c r="E29" s="22">
-        <f>'Financial Data'!E10/'Financial Data'!E29</f>
-        <v/>
-      </c>
-      <c r="F29" s="22">
-        <f>'Financial Data'!F10/'Financial Data'!F29</f>
-        <v/>
-      </c>
-      <c r="G29" s="22">
-        <f>'Financial Data'!G10/'Financial Data'!G29</f>
-        <v/>
-      </c>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="22" t="n"/>
       <c r="I29" s="23" t="inlineStr">
         <is>
           <t>Revenue / Total Assets</t>
@@ -3297,26 +2421,11 @@
           <t>Net Profit Margin</t>
         </is>
       </c>
-      <c r="C33" s="16">
-        <f>C23</f>
-        <v/>
-      </c>
-      <c r="D33" s="16">
-        <f>D23</f>
-        <v/>
-      </c>
-      <c r="E33" s="16">
-        <f>E23</f>
-        <v/>
-      </c>
-      <c r="F33" s="16">
-        <f>F23</f>
-        <v/>
-      </c>
-      <c r="G33" s="16">
-        <f>G23</f>
-        <v/>
-      </c>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="16" t="n"/>
       <c r="I33" s="24" t="inlineStr">
         <is>
           <t>pull it from the Profitability block above</t>
@@ -3329,26 +2438,11 @@
           <t>x  Total Asset Turnover</t>
         </is>
       </c>
-      <c r="C34" s="22">
-        <f>C29</f>
-        <v/>
-      </c>
-      <c r="D34" s="22">
-        <f>D29</f>
-        <v/>
-      </c>
-      <c r="E34" s="22">
-        <f>E29</f>
-        <v/>
-      </c>
-      <c r="F34" s="22">
-        <f>F29</f>
-        <v/>
-      </c>
-      <c r="G34" s="22">
-        <f>G29</f>
-        <v/>
-      </c>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="n"/>
       <c r="I34" s="24" t="inlineStr">
         <is>
           <t>pull it from the Efficiency block above</t>
@@ -3361,26 +2455,11 @@
           <t>x  Equity Multiplier</t>
         </is>
       </c>
-      <c r="C35" s="22">
-        <f>C17</f>
-        <v/>
-      </c>
-      <c r="D35" s="22">
-        <f>D17</f>
-        <v/>
-      </c>
-      <c r="E35" s="22">
-        <f>E17</f>
-        <v/>
-      </c>
-      <c r="F35" s="22">
-        <f>F17</f>
-        <v/>
-      </c>
-      <c r="G35" s="22">
-        <f>G17</f>
-        <v/>
-      </c>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="22" t="n"/>
+      <c r="F35" s="22" t="n"/>
+      <c r="G35" s="22" t="n"/>
       <c r="I35" s="24" t="inlineStr">
         <is>
           <t>pull it from the Leverage block above</t>
@@ -3392,26 +2471,11 @@
         <f>  ROE (from DuPont)</f>
         <v/>
       </c>
-      <c r="C36" s="16">
-        <f>C33*C34*C35</f>
-        <v/>
-      </c>
-      <c r="D36" s="16">
-        <f>D33*D34*D35</f>
-        <v/>
-      </c>
-      <c r="E36" s="16">
-        <f>E33*E34*E35</f>
-        <v/>
-      </c>
-      <c r="F36" s="16">
-        <f>F33*F34*F35</f>
-        <v/>
-      </c>
-      <c r="G36" s="16">
-        <f>G33*G34*G35</f>
-        <v/>
-      </c>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
+      <c r="G36" s="16" t="n"/>
       <c r="I36" s="24" t="inlineStr">
         <is>
           <t>multiply the three rows above</t>
@@ -3424,26 +2488,11 @@
           <t>ROE (from Profitability block)</t>
         </is>
       </c>
-      <c r="C37" s="16">
-        <f>C25</f>
-        <v/>
-      </c>
-      <c r="D37" s="16">
-        <f>D25</f>
-        <v/>
-      </c>
-      <c r="E37" s="16">
-        <f>E25</f>
-        <v/>
-      </c>
-      <c r="F37" s="16">
-        <f>F25</f>
-        <v/>
-      </c>
-      <c r="G37" s="16">
-        <f>G25</f>
-        <v/>
-      </c>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="16" t="n"/>
       <c r="I37" s="24" t="inlineStr">
         <is>
           <t>link to the ROE row above</t>
@@ -3456,26 +2505,11 @@
           <t>CHECK: difference</t>
         </is>
       </c>
-      <c r="C38" s="26">
-        <f>C36-C37</f>
-        <v/>
-      </c>
-      <c r="D38" s="26">
-        <f>D36-D37</f>
-        <v/>
-      </c>
-      <c r="E38" s="26">
-        <f>E36-E37</f>
-        <v/>
-      </c>
-      <c r="F38" s="26">
-        <f>F36-F37</f>
-        <v/>
-      </c>
-      <c r="G38" s="26">
-        <f>G36-G37</f>
-        <v/>
-      </c>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+      <c r="E38" s="26" t="n"/>
+      <c r="F38" s="26" t="n"/>
+      <c r="G38" s="26" t="n"/>
       <c r="I38" s="24" t="inlineStr">
         <is>
           <t>the two ROE rows minus each other - must be 0.00%</t>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -2076,7 +2076,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Fourteen ratios, all five years, plus the DuPont decomposition.</t>
+          <t>Fifteen ratios, all five years, plus the DuPont decomposition.</t>
         </is>
       </c>
     </row>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -568,6 +568,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -582,6 +584,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
@@ -592,7 +595,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Yellow cells = you type the number in.</t>
+          <t xml:space="preserve">   Blue cells = your company’s reported figures. Leave them alone.</t>
         </is>
       </c>
       <c r="B9" s="7" t="n"/>
@@ -605,6 +608,8 @@
       </c>
       <c r="B10" s="8" t="n"/>
     </row>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
@@ -636,10 +641,12 @@
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ratios  -  Fifteen ratios plus the DuPont decomposition.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">   Ratios  -  Fourteen ratios plus the DuPont decomposition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -654,6 +661,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
@@ -668,6 +676,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
@@ -696,6 +705,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
@@ -717,6 +727,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
@@ -731,6 +742,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
@@ -769,7 +781,7 @@
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   [ ]  You have not left the TTM column in by mistake</t>
+          <t xml:space="preserve">   [ ]  Interest Expense is positive and the Sources tab matches what you expected</t>
         </is>
       </c>
     </row>
@@ -801,7 +813,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Financial Data  -  type your five years here</t>
+          <t>Financial Data  -  five years, as filed with the SEC</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -816,7 +828,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>This is the only sheet where you type numbers. Everything else links back to it.</t>
+          <t>Already filled in for you. Read it and check it, but do not retype it. Every other sheet links back here.</t>
         </is>
       </c>
     </row>
@@ -852,11 +864,12 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Data source (paste the URL)</t>
+          <t>Data source</t>
         </is>
       </c>
       <c r="C6" s="10" t="n"/>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
@@ -984,6 +997,7 @@
       <c r="F18" s="13" t="n"/>
       <c r="G18" s="13" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
@@ -1099,6 +1113,7 @@
       <c r="F29" s="13" t="n"/>
       <c r="G29" s="13" t="n"/>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
@@ -1202,6 +1217,7 @@
       <c r="F39" s="13" t="n"/>
       <c r="G39" s="13" t="n"/>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
@@ -1281,6 +1297,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
@@ -1428,6 +1449,7 @@
       <c r="F18" s="16" t="n"/>
       <c r="G18" s="16" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
@@ -1548,6 +1570,7 @@
       <c r="F29" s="16" t="n"/>
       <c r="G29" s="16" t="n"/>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
@@ -1698,6 +1721,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -1866,6 +1890,8 @@
       <c r="F15" s="16" t="n"/>
       <c r="G15" s="16" t="n"/>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
@@ -2076,10 +2102,15 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Fifteen ratios, all five years, plus the DuPont decomposition.</t>
-        </is>
-      </c>
-    </row>
+          <t>Fourteen ratios, all five years, plus the DuPont decomposition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
@@ -2165,6 +2196,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
@@ -2240,6 +2272,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
@@ -2332,6 +2365,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
@@ -2373,6 +2407,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
@@ -2516,10 +2551,11 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>If the CHECK row is not zero, one of the three components is wrong. That is the point of the check - it catches your error before I do.</t>
+          <t>If the CHECK row is not zero, one of the three components is wrong. The check exists so you find your own error before I do.</t>
         </is>
       </c>
     </row>
